--- a/src/test/resources/DataDriven/LoginPageNew.xlsx
+++ b/src/test/resources/DataDriven/LoginPageNew.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2445" windowWidth="12540" windowHeight="4110" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="2445" windowWidth="12540" windowHeight="4110" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="262">
   <si>
     <t>Password</t>
   </si>
@@ -433,9 +434,6 @@
     <t>agreement</t>
   </si>
   <si>
-    <t>D:\\Latest Docs and Downloads Backup\\Rentalagrement3.pdf</t>
-  </si>
-  <si>
     <t>Karnataka</t>
   </si>
   <si>
@@ -593,6 +591,219 @@
   </si>
   <si>
     <t>Transaction Details</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Password@2</t>
+  </si>
+  <si>
+    <t>Citizen registration</t>
+  </si>
+  <si>
+    <t>Confirm Password</t>
+  </si>
+  <si>
+    <t>citizenuser1</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>RMI User</t>
+  </si>
+  <si>
+    <t>citizenuser3</t>
+  </si>
+  <si>
+    <t>citizenuser4</t>
+  </si>
+  <si>
+    <t>Bank Details</t>
+  </si>
+  <si>
+    <t>Acc No</t>
+  </si>
+  <si>
+    <t>Confirm Acc No</t>
+  </si>
+  <si>
+    <t>IFSC</t>
+  </si>
+  <si>
+    <t>Con IFSC</t>
+  </si>
+  <si>
+    <t>Conf Pan</t>
+  </si>
+  <si>
+    <t>Upload</t>
+  </si>
+  <si>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t>MNBPD6543N</t>
+  </si>
+  <si>
+    <t>HDFC0000077</t>
+  </si>
+  <si>
+    <t>EID</t>
+  </si>
+  <si>
+    <t>retr@trer.yrt</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>RMITESTUSER</t>
+  </si>
+  <si>
+    <t>D:\\Latest Docs and Downloads Backup\\140820231058130005396090.pdf</t>
+  </si>
+  <si>
+    <t>eMitra</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Municipality</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>Urban</t>
+  </si>
+  <si>
+    <t>435678</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>Applicant Info</t>
+  </si>
+  <si>
+    <t>Appl name</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Marital status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address </t>
+  </si>
+  <si>
+    <t>Aadhaar</t>
+  </si>
+  <si>
+    <t>Bank Detail proof</t>
+  </si>
+  <si>
+    <t>Educational proof</t>
+  </si>
+  <si>
+    <t>kiosk</t>
+  </si>
+  <si>
+    <t>present business</t>
+  </si>
+  <si>
+    <t>Police verification no</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>01-MAY-2007</t>
+  </si>
+  <si>
+    <t>Ajmer</t>
+  </si>
+  <si>
+    <t>lkjpm8765v</t>
+  </si>
+  <si>
+    <t>987654323456</t>
+  </si>
+  <si>
+    <t>Cancelled Cheque</t>
+  </si>
+  <si>
+    <t>Graduation</t>
+  </si>
+  <si>
+    <t>Existing CSC</t>
+  </si>
+  <si>
+    <t>23423423</t>
+  </si>
+  <si>
+    <t>AJMER</t>
+  </si>
+  <si>
+    <t>WARD NO 01</t>
+  </si>
+  <si>
+    <t>Ajmer,Rajasthan</t>
+  </si>
+  <si>
+    <t>9876556789</t>
+  </si>
+  <si>
+    <t>KAKBN0118</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Avg Bil</t>
+  </si>
+  <si>
+    <t>specific req</t>
+  </si>
+  <si>
+    <t>Doc</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>TestUser</t>
+  </si>
+  <si>
+    <t>Jaipur,Rajasthan</t>
+  </si>
+  <si>
+    <t>Normal Requirements</t>
+  </si>
+  <si>
+    <t>E:\\Latest Docs and Downloads Backup\\123.pdf</t>
+  </si>
+  <si>
+    <t>E:\\Ramya\\Ramya Downloads\\190214.pdf</t>
+  </si>
+  <si>
+    <t>E:\\Latest Docs and Downloads Backup\\Rentalagrement3.pdf</t>
   </si>
 </sst>
 </file>
@@ -699,7 +910,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -735,6 +946,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1056,10 +1272,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -1114,17 +1330,17 @@
         <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1256,7 +1472,7 @@
         <v>31</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>107</v>
@@ -1313,17 +1529,17 @@
         <v>41</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1355,10 +1571,10 @@
         <v>51</v>
       </c>
       <c r="F19" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="17" t="s">
         <v>153</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1373,10 +1589,10 @@
         <v>52</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1407,26 +1623,26 @@
       <c r="A24" s="3"/>
       <c r="B24" s="2"/>
       <c r="F24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2"/>
       <c r="C25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1437,10 +1653,10 @@
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="F27" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1451,10 +1667,10 @@
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1529,7 +1745,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>48</v>
@@ -1553,7 +1769,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,7 +1803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G21"/>
+  <dimension ref="B1:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -1597,14 +1813,46 @@
     <col min="5" max="5" width="15.85546875" customWidth="1"/>
     <col min="6" max="6" width="32.28515625" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" customWidth="1"/>
+    <col min="13" max="13" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B1" s="23" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G2" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="17" t="s">
         <v>68</v>
       </c>
@@ -1617,8 +1865,29 @@
       <c r="E3" s="17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>72</v>
       </c>
@@ -1632,7 +1901,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="23" t="s">
         <v>86</v>
       </c>
@@ -1643,7 +1912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="17" t="s">
         <v>68</v>
       </c>
@@ -1663,7 +1932,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>80</v>
       </c>
@@ -1683,12 +1952,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>85</v>
       </c>
@@ -1708,7 +1977,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>84</v>
       </c>
@@ -1743,19 +2012,19 @@
       <c r="D20" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="31"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="14" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1770,7 +2039,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1910,7 +2179,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1930,19 +2199,19 @@
         <v>136</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>89</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>77</v>
@@ -1954,149 +2223,461 @@
         <v>137</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>40</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="L9" s="6"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="E13" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" t="s">
         <v>187</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" s="23" t="s">
         <v>188</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C21" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D23" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D24" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B14" r:id="rId1"/>
+    <hyperlink ref="F23" r:id="rId2"/>
+    <hyperlink ref="G23" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="157" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="157" orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="54.85546875" customWidth="1"/>
+    <col min="8" max="8" width="62.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="157" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>